--- a/docs/carga-ajuste-realidad-entregas-202605051851.xlsx
+++ b/docs/carga-ajuste-realidad-entregas-202605051851.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Enrique Arenas\Documents\Control de Entregas - Formatto\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927A3CE4-B87B-4D02-9F4E-E8FE58CCE1E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D192BE-025C-4A90-BB1F-04FEA8DC5F2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29610" yWindow="-120" windowWidth="28110" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
